--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MT\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7007D111-608D-43D1-B88B-AC0DA59CDBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A9EEE9-4E1C-42FD-ACE0-C76F74844C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12195" yWindow="225" windowWidth="16605" windowHeight="17055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -533,12 +533,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -546,15 +546,15 @@
         <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45237</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,55 +562,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -627,13 +627,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -665,23 +665,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -705,7 +705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -721,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -845,13 +845,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
